--- a/partners.xlsx
+++ b/partners.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="129">
   <si>
     <t>지역</t>
   </si>
@@ -25,10 +25,16 @@
     <t>강원 강릉</t>
   </si>
   <si>
+    <t>비사이드그라운드</t>
+  </si>
+  <si>
+    <t>강원도 강릉시 용지로 136</t>
+  </si>
+  <si>
     <t>카페 안드로메다</t>
   </si>
   <si>
-    <t>강원 강릉시 하슬라로20번길 8 1층</t>
+    <t>강원도 강릉시 하슬라로20번길 8 1층</t>
   </si>
   <si>
     <t>경기 안산</t>
@@ -37,16 +43,31 @@
     <t>이스턴문</t>
   </si>
   <si>
-    <t>경기 안산시 상록구 한양대학로 35 3층 이스턴문</t>
+    <t>경기도 안산시 상록구 한양대학로 35 3층 이스턴문</t>
   </si>
   <si>
     <t>경기 평택</t>
   </si>
   <si>
-    <t>와일드그라스 커피로스터리 비전, 도상</t>
-  </si>
-  <si>
-    <t>경기 평택시 평택3로 89 1층 와일드그라스</t>
+    <t>와일드그라스 커피로스터리 비전</t>
+  </si>
+  <si>
+    <t>경기도 평택시 평택3로 89 1층 와일드그라스</t>
+  </si>
+  <si>
+    <t>와일드그라스 커피로스터리 도상</t>
+  </si>
+  <si>
+    <t>경기도 평택시 원평로105번길 31 1층</t>
+  </si>
+  <si>
+    <t>경남 양산</t>
+  </si>
+  <si>
+    <t>히떼로스터리 원동점</t>
+  </si>
+  <si>
+    <t>경상남도 양산시 원동면 화제로 190 1층</t>
   </si>
   <si>
     <t>경남 진주</t>
@@ -55,7 +76,7 @@
     <t>목요일오후네시</t>
   </si>
   <si>
-    <t>경남 진주시 강남로247번길 6-1</t>
+    <t>경남 진주시 강남로247번길 6-1, 1층 목요일오후네시</t>
   </si>
   <si>
     <t>경남 통영</t>
@@ -76,13 +97,22 @@
     <t>경남 합천군 합천읍 충효로 77-20</t>
   </si>
   <si>
+    <t>대구</t>
+  </si>
+  <si>
+    <t>소설 오일장 with 데스커</t>
+  </si>
+  <si>
+    <t>대구시 수성구 무학로 113, desker lounge 2층 카페</t>
+  </si>
+  <si>
     <t>대전</t>
   </si>
   <si>
     <t>다다르다</t>
   </si>
   <si>
-    <t>대전 중구 중교로73번길 6 1층</t>
+    <t>대전시 중구 중교로73번길 6 1층</t>
   </si>
   <si>
     <t>대전혜광학교기업 카페뜰 3호점</t>
@@ -112,19 +142,19 @@
     <t>사마브루잉</t>
   </si>
   <si>
-    <t>대전시 서구 사마1길 14 1층(도마동 101-3)</t>
+    <t>대전 서구 사마1길 14 1층(도마동 101-3)</t>
   </si>
   <si>
     <t>카페 에이치h</t>
   </si>
   <si>
-    <t>대전시 유성구 동서대로 130 1층</t>
+    <t>대전 유성구 동서대로 130 1층</t>
   </si>
   <si>
     <t>바베트의 만찬(서점)</t>
   </si>
   <si>
-    <t>대전시 서구 계룡로367번길 106 1층</t>
+    <t>대전 서구 계룡로367번길 106 1층</t>
   </si>
   <si>
     <t>부산</t>
@@ -133,34 +163,25 @@
     <t>레이지모먼트커피스탠드</t>
   </si>
   <si>
-    <t>부산시 동래구 온천천로285번길 19 지전빌딩 2층</t>
+    <t>부산 동래구 온천천로285번길 19 지전빌딩 2층</t>
   </si>
   <si>
     <t>히떼로스터리 광안점</t>
   </si>
   <si>
-    <t xml:space="preserve">부산시 수영구 수영로 510번길 57 2층 </t>
+    <t>부산시 수영구 수영로 510번길 57 2층</t>
   </si>
   <si>
     <t>히떼로스터리 강서점</t>
   </si>
   <si>
-    <t xml:space="preserve">부산시 강서구 공항로 475 2층 </t>
-  </si>
-  <si>
-    <t>경남 양산</t>
-  </si>
-  <si>
-    <t>히떼로스터리 원동점</t>
-  </si>
-  <si>
-    <t>경상남도 양산시 원동면 화제로 190 1층</t>
+    <t>부산시 강서구 공항로 475 2층</t>
   </si>
   <si>
     <t>히떼로스터리 전포점</t>
   </si>
   <si>
-    <t>부산시 부산진구 동성로 59</t>
+    <t>부산광역시 부산진구 동성로 59</t>
   </si>
   <si>
     <t>서울 광진</t>
@@ -169,7 +190,16 @@
     <t>올리카</t>
   </si>
   <si>
-    <t>서울시 광진구 천호대로109길 53 1층 101호</t>
+    <t>서울 광진구 천호대로109길 53 1층 101호</t>
+  </si>
+  <si>
+    <t>서울 금천</t>
+  </si>
+  <si>
+    <t>칩스</t>
+  </si>
+  <si>
+    <t>서울시 금천구 두산로 9길 5 1층, 칩스</t>
   </si>
   <si>
     <t>서울 노원</t>
@@ -178,7 +208,7 @@
     <t>비스킷 플로어</t>
   </si>
   <si>
-    <t>서울시 노원구 동일로190길 8 1층</t>
+    <t>서울 노원구 동일로190길 8 1층</t>
   </si>
   <si>
     <t>서울 동대문</t>
@@ -187,7 +217,7 @@
     <t>이문동커피집</t>
   </si>
   <si>
-    <t>서울시 동대문구 이문로25길 39 1층</t>
+    <t>서울 동대문구 이문로25길 39 1층</t>
   </si>
   <si>
     <t>서울 마포</t>
@@ -196,13 +226,25 @@
     <t>써밋컬쳐</t>
   </si>
   <si>
-    <t>서울시 마포구 신촌로14안길 11 엘루체 102호</t>
+    <t>서울 마포구 신촌로14안길 11 엘루체 102호</t>
   </si>
   <si>
     <t>후엘고</t>
   </si>
   <si>
-    <t>서울시 마포구 마포대로11길 118 1층 후엘고</t>
+    <t>서울 마포구 마포대로11길 118 1층 후엘고</t>
+  </si>
+  <si>
+    <t>하하사</t>
+  </si>
+  <si>
+    <t>서울 마포구 동교로 131 3층</t>
+  </si>
+  <si>
+    <t>핏자라운지</t>
+  </si>
+  <si>
+    <t>서울시 마포구 망원동 400-20, 2층 핏자워크라운지</t>
   </si>
   <si>
     <t>서울 서초</t>
@@ -211,7 +253,7 @@
     <t>카페모호</t>
   </si>
   <si>
-    <t>서울시 서초구 양재천로7길 1 1층</t>
+    <t>서울 서초구 양재천로7길 1 1층</t>
   </si>
   <si>
     <t>서울 성동</t>
@@ -220,37 +262,49 @@
     <t>브루잉 세레모니</t>
   </si>
   <si>
-    <t>서울시 성동구 연무장5가길 22-1 1층</t>
+    <t>서울 성동구 연무장5가길 22-1 1층</t>
   </si>
   <si>
     <t>메쉬커피</t>
   </si>
   <si>
-    <t>서울시 성동구 서울숲길 43</t>
+    <t>서울 성동구 서울숲길 43</t>
   </si>
   <si>
     <t>오루베</t>
   </si>
   <si>
-    <t>서울시 성동구 왕십리로31길 8</t>
+    <t>서울 성동구 왕십리로31길 8</t>
   </si>
   <si>
     <t>브로벨커피</t>
   </si>
   <si>
-    <t>서울시 성동구 뚝섬로 413 1층</t>
+    <t>서울 성동구 뚝섬로 413 1층</t>
   </si>
   <si>
     <t>위스탠커피</t>
   </si>
   <si>
-    <t>서울시 성동구 뚝섬로13길 38 상상플래닛 1층 위스탠커피</t>
+    <t>서울 성동구 뚝섬로13길 38 상상플래닛 1층 위스탠커피</t>
   </si>
   <si>
     <t>어페어커피</t>
   </si>
   <si>
-    <t>서울시 성동구 성수이로6길 11</t>
+    <t>성동구 성수이로 6길 11 1층 어페어커피</t>
+  </si>
+  <si>
+    <t>미닛로스터리</t>
+  </si>
+  <si>
+    <t>서울시 성동구 왕십리로 343 1층 미닛 로스터리</t>
+  </si>
+  <si>
+    <t>블루제이커피스페이스</t>
+  </si>
+  <si>
+    <t>서울 성동구 무학봉15길 20, 1층 블루제이커피스페이스</t>
   </si>
   <si>
     <t>서울 용산</t>
@@ -259,13 +313,13 @@
     <t>로헬그</t>
   </si>
   <si>
-    <t>서울시 용산구 두텁바위로1나길 7 1층 101호 로헬그</t>
+    <t>서울 용산구 두텁바위로1나길 7 1층 101호 로헬그</t>
   </si>
   <si>
     <t>후암연립</t>
   </si>
   <si>
-    <t>서울시 용산구 두텁바위로1가길 47 후암연립</t>
+    <t>서울 용산구 두텁바위로1가길 47 후암연립</t>
   </si>
   <si>
     <t>서울 종로</t>
@@ -274,13 +328,13 @@
     <t>카페보부</t>
   </si>
   <si>
-    <t>서울시 종로구 율곡로1길 42 1층 카페보부</t>
+    <t>서울 종로구 율곡로1길 42 1층 카페보부</t>
   </si>
   <si>
     <t>서울 중구</t>
   </si>
   <si>
-    <t>서울시 중구 장충단로 193-1 1층</t>
+    <t>서울 중구 장충단로 193-1 1층 어페어커피 장충점</t>
   </si>
   <si>
     <t>세종</t>
@@ -289,7 +343,7 @@
     <t>빈스먼스</t>
   </si>
   <si>
-    <t>세종시 조치원읍 충현로 59 201호</t>
+    <t>세종 조치원읍 충현로 59 201호</t>
   </si>
   <si>
     <t>울산</t>
@@ -298,7 +352,7 @@
     <t>시그너스커피</t>
   </si>
   <si>
-    <t>울산시 남구 번영로119 1층 시그너스커피</t>
+    <t>울산광역시 남구 번영로119 1층 시그너스커피</t>
   </si>
   <si>
     <t>인천</t>
@@ -307,36 +361,30 @@
     <t>송도커피</t>
   </si>
   <si>
-    <t>인천시 연수구 컨벤시아대로 60 푸르지오월드마크 2단지 1층 149호 송도커피</t>
+    <t>인천 연수구 컨벤시아대로 60 푸르지오월드마크 2단지 1층 149호 송도커피</t>
   </si>
   <si>
     <t>디벨로핑룸</t>
   </si>
   <si>
-    <t>인천시 서구 원적로7번길 1</t>
+    <t>인천광역시 서구 원적로7번길 1</t>
   </si>
   <si>
     <t>유니크롱</t>
   </si>
   <si>
-    <t>인천시 연수구 송도과학로27번길 55 롯데캐슬캠퍼스타운 상가 C-110호</t>
+    <t>인천 연수구 송도과학로27번길 55 롯데캐슬캠퍼스타운 상가 C-110호</t>
   </si>
   <si>
     <t>디저트39 송도캠퍼스타운점</t>
   </si>
   <si>
-    <t>인천시 연수구 송도과학로27번길 55 캠퍼스타운 애비뉴</t>
+    <t>인천 연수구 송도과학로27번길 55 캠퍼스타운 애비뉴</t>
   </si>
   <si>
     <t>전북 전주</t>
   </si>
   <si>
-    <t>포도시</t>
-  </si>
-  <si>
-    <t>전북 전주시 완산구 전주객사2길 92 1층</t>
-  </si>
-  <si>
     <t>라부</t>
   </si>
   <si>
@@ -349,22 +397,15 @@
     <t>오세요커피</t>
   </si>
   <si>
-    <t>제주도 서귀포시 신중로13번길 17 1층</t>
-  </si>
-  <si>
-    <t>블루제이커피스페이스</t>
-  </si>
-  <si>
-    <t>서울시 성동구 무학봉15길 20, 1층 블루제이커피스페이스</t>
+    <t>제주 서귀포시 신중로13번길 17 1층</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="0" formatCode="General"/>
-    <numFmt numFmtId="59" formatCode="#,##0;(#,##0)"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -389,21 +430,15 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="10"/>
-        <bgColor auto="1"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="15">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -426,186 +461,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="hair">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="hair">
-        <color indexed="8"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="8"/>
-      </left>
-      <right style="hair">
-        <color indexed="8"/>
-      </right>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="hair">
-        <color indexed="8"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="hair">
-        <color indexed="8"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="hair">
-        <color indexed="8"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top style="thin">
-        <color indexed="9"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="9"/>
-      </left>
-      <right style="thin">
-        <color indexed="9"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="9"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -615,65 +477,14 @@
     <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="9" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="11" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" borderId="12" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="13" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="59" fontId="0" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -693,7 +504,6 @@
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
       <rgbColor rgb="ffaaaaaa"/>
-      <rgbColor rgb="ffffffff"/>
     </indexedColors>
   </colors>
 </styleSheet>
@@ -1728,7 +1538,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E48"/>
+  <dimension ref="A1:E53"/>
   <sheetFormatPr defaultColWidth="12.6667" defaultRowHeight="15.75" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="12.6719" style="1" customWidth="1"/>
@@ -1739,617 +1549,688 @@
     <col min="6" max="16384" width="12.6719" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.65" customHeight="1">
+    <row r="1" ht="15.65" customHeight="1">
       <c r="A1" s="2"/>
       <c r="B1" t="s" s="3">
         <v>0</v>
       </c>
-      <c r="C1" t="s" s="4">
+      <c r="C1" t="s" s="3">
         <v>1</v>
       </c>
-      <c r="D1" t="s" s="5">
+      <c r="D1" t="s" s="3">
         <v>2</v>
       </c>
       <c r="E1" s="2"/>
     </row>
-    <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="6"/>
-      <c r="B2" t="s" s="7">
+    <row r="2" ht="15.65" customHeight="1">
+      <c r="A2" s="2"/>
+      <c r="B2" t="s" s="4">
         <v>3</v>
       </c>
-      <c r="C2" t="s" s="7">
+      <c r="C2" t="s" s="4">
         <v>4</v>
       </c>
-      <c r="D2" t="s" s="8">
+      <c r="D2" t="s" s="4">
         <v>5</v>
       </c>
-      <c r="E2" s="9"/>
-    </row>
-    <row r="3" ht="13.65" customHeight="1">
-      <c r="A3" s="6"/>
-      <c r="B3" t="s" s="7">
+      <c r="E2" s="2"/>
+    </row>
+    <row r="3" ht="15.65" customHeight="1">
+      <c r="A3" s="2"/>
+      <c r="B3" t="s" s="4">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s" s="4">
         <v>6</v>
       </c>
-      <c r="C3" t="s" s="7">
+      <c r="D3" t="s" s="4">
         <v>7</v>
       </c>
-      <c r="D3" t="s" s="10">
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" ht="15.65" customHeight="1">
+      <c r="A4" s="2"/>
+      <c r="B4" t="s" s="4">
         <v>8</v>
       </c>
-      <c r="E3" s="9"/>
-    </row>
-    <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="6"/>
-      <c r="B4" t="s" s="7">
+      <c r="C4" t="s" s="4">
         <v>9</v>
       </c>
-      <c r="C4" t="s" s="7">
+      <c r="D4" t="s" s="4">
         <v>10</v>
       </c>
-      <c r="D4" t="s" s="8">
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" ht="15.65" customHeight="1">
+      <c r="A5" s="2"/>
+      <c r="B5" t="s" s="4">
         <v>11</v>
       </c>
-      <c r="E4" s="9"/>
-    </row>
-    <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="6"/>
-      <c r="B5" t="s" s="7">
+      <c r="C5" t="s" s="4">
         <v>12</v>
       </c>
-      <c r="C5" t="s" s="7">
+      <c r="D5" t="s" s="4">
         <v>13</v>
       </c>
-      <c r="D5" t="s" s="8">
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" ht="15.65" customHeight="1">
+      <c r="A6" s="2"/>
+      <c r="B6" t="s" s="4">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s" s="4">
         <v>14</v>
       </c>
-      <c r="E5" s="9"/>
-    </row>
-    <row r="6" ht="15" customHeight="1">
-      <c r="A6" s="6"/>
-      <c r="B6" t="s" s="7">
+      <c r="D6" t="s" s="4">
         <v>15</v>
       </c>
-      <c r="C6" t="s" s="7">
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" ht="15.65" customHeight="1">
+      <c r="A7" s="2"/>
+      <c r="B7" t="s" s="4">
         <v>16</v>
       </c>
-      <c r="D6" t="s" s="8">
+      <c r="C7" t="s" s="4">
         <v>17</v>
       </c>
-      <c r="E6" s="9"/>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="6"/>
-      <c r="B7" t="s" s="7">
+      <c r="D7" t="s" s="4">
         <v>18</v>
       </c>
-      <c r="C7" t="s" s="7">
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" ht="15.65" customHeight="1">
+      <c r="A8" s="2"/>
+      <c r="B8" t="s" s="4">
         <v>19</v>
       </c>
-      <c r="D7" t="s" s="8">
+      <c r="C8" t="s" s="4">
         <v>20</v>
       </c>
-      <c r="E7" s="9"/>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" s="6"/>
-      <c r="B8" t="s" s="7">
+      <c r="D8" t="s" s="4">
         <v>21</v>
       </c>
-      <c r="C8" t="s" s="7">
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" ht="15.65" customHeight="1">
+      <c r="A9" s="2"/>
+      <c r="B9" t="s" s="4">
         <v>22</v>
       </c>
-      <c r="D8" t="s" s="8">
+      <c r="C9" t="s" s="4">
         <v>23</v>
       </c>
-      <c r="E8" s="9"/>
-    </row>
-    <row r="9" ht="13.65" customHeight="1">
-      <c r="A9" s="6"/>
-      <c r="B9" t="s" s="7">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s" s="7">
+      <c r="D9" t="s" s="4">
         <v>24</v>
       </c>
-      <c r="D9" t="s" s="10">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" ht="15.65" customHeight="1">
+      <c r="A10" s="2"/>
+      <c r="B10" t="s" s="4">
         <v>25</v>
       </c>
-      <c r="E9" s="9"/>
-    </row>
-    <row r="10" ht="13.65" customHeight="1">
-      <c r="A10" s="6"/>
-      <c r="B10" t="s" s="7">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s" s="7">
+      <c r="C10" t="s" s="4">
         <v>26</v>
       </c>
-      <c r="D10" t="s" s="10">
+      <c r="D10" t="s" s="4">
         <v>27</v>
       </c>
-      <c r="E10" s="9"/>
-    </row>
-    <row r="11" ht="13.65" customHeight="1">
-      <c r="A11" s="6"/>
-      <c r="B11" t="s" s="7">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s" s="7">
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" ht="15.65" customHeight="1">
+      <c r="A11" s="2"/>
+      <c r="B11" t="s" s="4">
         <v>28</v>
       </c>
-      <c r="D11" t="s" s="10">
+      <c r="C11" t="s" s="4">
         <v>29</v>
       </c>
-      <c r="E11" s="9"/>
-    </row>
-    <row r="12" ht="13.65" customHeight="1">
-      <c r="A12" s="6"/>
-      <c r="B12" t="s" s="7">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s" s="7">
+      <c r="D11" t="s" s="4">
         <v>30</v>
       </c>
-      <c r="D12" t="s" s="10">
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" ht="15.65" customHeight="1">
+      <c r="A12" s="2"/>
+      <c r="B12" t="s" s="4">
         <v>31</v>
       </c>
-      <c r="E12" s="9"/>
-    </row>
-    <row r="13" ht="13.65" customHeight="1">
-      <c r="A13" s="6"/>
-      <c r="B13" t="s" s="7">
-        <v>21</v>
-      </c>
-      <c r="C13" t="s" s="7">
+      <c r="C12" t="s" s="4">
         <v>32</v>
       </c>
-      <c r="D13" t="s" s="11">
+      <c r="D12" t="s" s="4">
         <v>33</v>
       </c>
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" ht="15.65" customHeight="1">
+      <c r="A13" s="2"/>
+      <c r="B13" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C13" t="s" s="4">
+        <v>34</v>
+      </c>
+      <c r="D13" t="s" s="4">
+        <v>35</v>
+      </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="6"/>
-      <c r="B14" t="s" s="7">
-        <v>21</v>
-      </c>
-      <c r="C14" t="s" s="7">
-        <v>34</v>
-      </c>
-      <c r="D14" t="s" s="8">
-        <v>35</v>
-      </c>
-      <c r="E14" s="9"/>
-    </row>
-    <row r="15" ht="15" customHeight="1">
-      <c r="A15" s="6"/>
-      <c r="B15" t="s" s="7">
-        <v>21</v>
-      </c>
-      <c r="C15" t="s" s="7">
+    <row r="14" ht="15.65" customHeight="1">
+      <c r="A14" s="2"/>
+      <c r="B14" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s" s="4">
         <v>36</v>
       </c>
-      <c r="D15" t="s" s="8">
+      <c r="D14" t="s" s="4">
         <v>37</v>
       </c>
-      <c r="E15" s="9"/>
-    </row>
-    <row r="16" ht="15" customHeight="1">
-      <c r="A16" s="6"/>
-      <c r="B16" t="s" s="7">
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" ht="15.65" customHeight="1">
+      <c r="A15" s="2"/>
+      <c r="B15" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C15" t="s" s="4">
         <v>38</v>
       </c>
-      <c r="C16" t="s" s="7">
+      <c r="D15" t="s" s="4">
         <v>39</v>
       </c>
-      <c r="D16" t="s" s="8">
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" ht="15.65" customHeight="1">
+      <c r="A16" s="2"/>
+      <c r="B16" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C16" t="s" s="4">
         <v>40</v>
       </c>
-      <c r="E16" s="9"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="6"/>
-      <c r="B17" t="s" s="7">
-        <v>38</v>
-      </c>
-      <c r="C17" t="s" s="7">
+      <c r="D16" t="s" s="4">
         <v>41</v>
       </c>
-      <c r="D17" t="s" s="8">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" ht="15.65" customHeight="1">
+      <c r="A17" s="2"/>
+      <c r="B17" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C17" t="s" s="4">
         <v>42</v>
       </c>
-      <c r="E17" s="9"/>
-    </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" s="6"/>
-      <c r="B18" t="s" s="7">
-        <v>38</v>
-      </c>
-      <c r="C18" t="s" s="7">
+      <c r="D17" t="s" s="4">
         <v>43</v>
       </c>
-      <c r="D18" t="s" s="8">
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" ht="15.65" customHeight="1">
+      <c r="A18" s="2"/>
+      <c r="B18" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C18" t="s" s="4">
         <v>44</v>
       </c>
-      <c r="E18" s="9"/>
-    </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" s="6"/>
-      <c r="B19" t="s" s="7">
+      <c r="D18" t="s" s="4">
         <v>45</v>
       </c>
-      <c r="C19" t="s" s="7">
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" ht="15.65" customHeight="1">
+      <c r="A19" s="2"/>
+      <c r="B19" t="s" s="4">
+        <v>31</v>
+      </c>
+      <c r="C19" t="s" s="4">
         <v>46</v>
       </c>
-      <c r="D19" t="s" s="8">
+      <c r="D19" t="s" s="4">
         <v>47</v>
       </c>
-      <c r="E19" s="9"/>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="6"/>
-      <c r="B20" t="s" s="7">
-        <v>38</v>
-      </c>
-      <c r="C20" t="s" s="7">
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" ht="15.65" customHeight="1">
+      <c r="A20" s="2"/>
+      <c r="B20" t="s" s="4">
         <v>48</v>
       </c>
-      <c r="D20" t="s" s="8">
+      <c r="C20" t="s" s="4">
         <v>49</v>
       </c>
-      <c r="E20" s="9"/>
-    </row>
-    <row r="21" ht="13.65" customHeight="1">
-      <c r="A21" s="6"/>
-      <c r="B21" t="s" s="7">
+      <c r="D20" t="s" s="4">
         <v>50</v>
       </c>
-      <c r="C21" t="s" s="7">
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" ht="15.65" customHeight="1">
+      <c r="A21" s="2"/>
+      <c r="B21" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="C21" t="s" s="4">
         <v>51</v>
       </c>
-      <c r="D21" t="s" s="10">
+      <c r="D21" t="s" s="4">
         <v>52</v>
       </c>
-      <c r="E21" s="9"/>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="6"/>
-      <c r="B22" t="s" s="7">
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" ht="15.65" customHeight="1">
+      <c r="A22" s="2"/>
+      <c r="B22" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="C22" t="s" s="4">
         <v>53</v>
       </c>
-      <c r="C22" t="s" s="7">
+      <c r="D22" t="s" s="4">
         <v>54</v>
       </c>
-      <c r="D22" t="s" s="8">
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" ht="15.65" customHeight="1">
+      <c r="A23" s="2"/>
+      <c r="B23" t="s" s="4">
+        <v>48</v>
+      </c>
+      <c r="C23" t="s" s="4">
         <v>55</v>
       </c>
-      <c r="E22" s="9"/>
-    </row>
-    <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="6"/>
-      <c r="B23" t="s" s="7">
+      <c r="D23" t="s" s="4">
         <v>56</v>
       </c>
-      <c r="C23" t="s" s="7">
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" ht="15.65" customHeight="1">
+      <c r="A24" s="2"/>
+      <c r="B24" t="s" s="4">
         <v>57</v>
       </c>
-      <c r="D23" t="s" s="8">
+      <c r="C24" t="s" s="4">
         <v>58</v>
       </c>
-      <c r="E23" s="9"/>
-    </row>
-    <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="6"/>
-      <c r="B24" t="s" s="7">
+      <c r="D24" t="s" s="4">
         <v>59</v>
       </c>
-      <c r="C24" t="s" s="7">
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" ht="15.65" customHeight="1">
+      <c r="A25" s="2"/>
+      <c r="B25" t="s" s="4">
         <v>60</v>
       </c>
-      <c r="D24" t="s" s="8">
+      <c r="C25" t="s" s="4">
         <v>61</v>
       </c>
-      <c r="E24" s="9"/>
-    </row>
-    <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="6"/>
-      <c r="B25" t="s" s="7">
-        <v>59</v>
-      </c>
-      <c r="C25" t="s" s="7">
+      <c r="D25" t="s" s="4">
         <v>62</v>
       </c>
-      <c r="D25" t="s" s="8">
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" ht="15.65" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" t="s" s="4">
         <v>63</v>
       </c>
-      <c r="E25" s="9"/>
-    </row>
-    <row r="26" ht="15" customHeight="1">
-      <c r="A26" s="6"/>
-      <c r="B26" t="s" s="7">
+      <c r="C26" t="s" s="4">
         <v>64</v>
       </c>
-      <c r="C26" t="s" s="7">
+      <c r="D26" t="s" s="4">
         <v>65</v>
       </c>
-      <c r="D26" t="s" s="8">
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" ht="15.65" customHeight="1">
+      <c r="A27" s="2"/>
+      <c r="B27" t="s" s="4">
         <v>66</v>
       </c>
-      <c r="E26" s="9"/>
-    </row>
-    <row r="27" ht="15" customHeight="1">
-      <c r="A27" s="6"/>
-      <c r="B27" t="s" s="7">
+      <c r="C27" t="s" s="4">
         <v>67</v>
       </c>
-      <c r="C27" t="s" s="7">
+      <c r="D27" t="s" s="4">
         <v>68</v>
       </c>
-      <c r="D27" t="s" s="8">
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" ht="15.65" customHeight="1">
+      <c r="A28" s="2"/>
+      <c r="B28" t="s" s="4">
         <v>69</v>
       </c>
-      <c r="E27" s="9"/>
-    </row>
-    <row r="28" ht="15" customHeight="1">
-      <c r="A28" s="6"/>
-      <c r="B28" t="s" s="7">
-        <v>67</v>
-      </c>
-      <c r="C28" t="s" s="7">
+      <c r="C28" t="s" s="4">
         <v>70</v>
       </c>
-      <c r="D28" t="s" s="8">
+      <c r="D28" t="s" s="4">
         <v>71</v>
       </c>
-      <c r="E28" s="9"/>
-    </row>
-    <row r="29" ht="15" customHeight="1">
-      <c r="A29" s="6"/>
-      <c r="B29" t="s" s="7">
-        <v>67</v>
-      </c>
-      <c r="C29" t="s" s="7">
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" ht="15.65" customHeight="1">
+      <c r="A29" s="2"/>
+      <c r="B29" t="s" s="4">
+        <v>69</v>
+      </c>
+      <c r="C29" t="s" s="4">
         <v>72</v>
       </c>
-      <c r="D29" t="s" s="8">
+      <c r="D29" t="s" s="4">
         <v>73</v>
       </c>
-      <c r="E29" s="9"/>
-    </row>
-    <row r="30" ht="15" customHeight="1">
-      <c r="A30" s="6"/>
-      <c r="B30" t="s" s="7">
-        <v>67</v>
-      </c>
-      <c r="C30" t="s" s="7">
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" ht="15.65" customHeight="1">
+      <c r="A30" s="2"/>
+      <c r="B30" t="s" s="4">
+        <v>69</v>
+      </c>
+      <c r="C30" t="s" s="4">
         <v>74</v>
       </c>
-      <c r="D30" t="s" s="8">
+      <c r="D30" t="s" s="4">
         <v>75</v>
       </c>
-      <c r="E30" s="9"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" t="s" s="7">
-        <v>67</v>
-      </c>
-      <c r="C31" t="s" s="7">
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" ht="15.65" customHeight="1">
+      <c r="A31" s="2"/>
+      <c r="B31" t="s" s="4">
+        <v>69</v>
+      </c>
+      <c r="C31" t="s" s="4">
         <v>76</v>
       </c>
-      <c r="D31" t="s" s="8">
+      <c r="D31" t="s" s="4">
         <v>77</v>
       </c>
-      <c r="E31" s="9"/>
-    </row>
-    <row r="32" ht="15" customHeight="1">
-      <c r="A32" s="6"/>
-      <c r="B32" t="s" s="7">
-        <v>67</v>
-      </c>
-      <c r="C32" t="s" s="7">
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" ht="15.65" customHeight="1">
+      <c r="A32" s="2"/>
+      <c r="B32" t="s" s="4">
         <v>78</v>
       </c>
-      <c r="D32" t="s" s="8">
+      <c r="C32" t="s" s="4">
         <v>79</v>
       </c>
-      <c r="E32" s="9"/>
-    </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="12"/>
-      <c r="B33" t="s" s="13">
+      <c r="D32" t="s" s="4">
         <v>80</v>
       </c>
-      <c r="C33" t="s" s="13">
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" ht="15.65" customHeight="1">
+      <c r="A33" s="2"/>
+      <c r="B33" t="s" s="4">
         <v>81</v>
       </c>
-      <c r="D33" t="s" s="14">
+      <c r="C33" t="s" s="4">
         <v>82</v>
       </c>
+      <c r="D33" t="s" s="4">
+        <v>83</v>
+      </c>
       <c r="E33" s="2"/>
     </row>
-    <row r="34" ht="15" customHeight="1">
-      <c r="A34" s="12"/>
-      <c r="B34" t="s" s="15">
-        <v>80</v>
-      </c>
-      <c r="C34" t="s" s="15">
-        <v>83</v>
-      </c>
-      <c r="D34" t="s" s="16">
+    <row r="34" ht="15.65" customHeight="1">
+      <c r="A34" s="2"/>
+      <c r="B34" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="C34" t="s" s="4">
         <v>84</v>
       </c>
+      <c r="D34" t="s" s="4">
+        <v>85</v>
+      </c>
       <c r="E34" s="2"/>
     </row>
-    <row r="35" ht="13.65" customHeight="1">
-      <c r="A35" s="12"/>
-      <c r="B35" t="s" s="15">
-        <v>85</v>
-      </c>
-      <c r="C35" t="s" s="15">
+    <row r="35" ht="15.65" customHeight="1">
+      <c r="A35" s="2"/>
+      <c r="B35" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="C35" t="s" s="4">
         <v>86</v>
       </c>
-      <c r="D35" t="s" s="17">
+      <c r="D35" t="s" s="4">
         <v>87</v>
       </c>
       <c r="E35" s="2"/>
     </row>
-    <row r="36" ht="15" customHeight="1">
-      <c r="A36" s="12"/>
-      <c r="B36" t="s" s="15">
+    <row r="36" ht="15.65" customHeight="1">
+      <c r="A36" s="2"/>
+      <c r="B36" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="C36" t="s" s="4">
         <v>88</v>
       </c>
-      <c r="C36" t="s" s="15">
-        <v>78</v>
-      </c>
-      <c r="D36" t="s" s="16">
+      <c r="D36" t="s" s="4">
         <v>89</v>
       </c>
       <c r="E36" s="2"/>
     </row>
-    <row r="37" ht="13.65" customHeight="1">
-      <c r="A37" s="12"/>
-      <c r="B37" t="s" s="15">
+    <row r="37" ht="15.65" customHeight="1">
+      <c r="A37" s="2"/>
+      <c r="B37" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="C37" t="s" s="4">
         <v>90</v>
       </c>
-      <c r="C37" t="s" s="15">
+      <c r="D37" t="s" s="4">
         <v>91</v>
       </c>
-      <c r="D37" t="s" s="17">
+      <c r="E37" s="2"/>
+    </row>
+    <row r="38" ht="15.65" customHeight="1">
+      <c r="A38" s="2"/>
+      <c r="B38" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="C38" t="s" s="4">
         <v>92</v>
       </c>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="12"/>
-      <c r="B38" t="s" s="15">
+      <c r="D38" t="s" s="4">
         <v>93</v>
       </c>
-      <c r="C38" t="s" s="15">
+      <c r="E38" s="2"/>
+    </row>
+    <row r="39" ht="15.65" customHeight="1">
+      <c r="A39" s="2"/>
+      <c r="B39" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="C39" t="s" s="4">
         <v>94</v>
       </c>
-      <c r="D38" t="s" s="16">
+      <c r="D39" t="s" s="4">
         <v>95</v>
       </c>
-      <c r="E38" s="2"/>
-    </row>
-    <row r="39" ht="27.3" customHeight="1">
-      <c r="A39" s="12"/>
-      <c r="B39" t="s" s="15">
+      <c r="E39" s="2"/>
+    </row>
+    <row r="40" ht="15.65" customHeight="1">
+      <c r="A40" s="2"/>
+      <c r="B40" t="s" s="4">
+        <v>81</v>
+      </c>
+      <c r="C40" t="s" s="4">
         <v>96</v>
       </c>
-      <c r="C39" t="s" s="15">
+      <c r="D40" t="s" s="4">
         <v>97</v>
       </c>
-      <c r="D39" t="s" s="16">
+      <c r="E40" s="2"/>
+    </row>
+    <row r="41" ht="15.65" customHeight="1">
+      <c r="A41" s="2"/>
+      <c r="B41" t="s" s="4">
         <v>98</v>
       </c>
-      <c r="E39" s="2"/>
-    </row>
-    <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="12"/>
-      <c r="B40" t="s" s="15">
-        <v>96</v>
-      </c>
-      <c r="C40" t="s" s="15">
+      <c r="C41" t="s" s="4">
         <v>99</v>
       </c>
-      <c r="D40" t="s" s="16">
+      <c r="D41" t="s" s="4">
         <v>100</v>
       </c>
-      <c r="E40" s="2"/>
-    </row>
-    <row r="41" ht="27.3" customHeight="1">
-      <c r="A41" s="12"/>
-      <c r="B41" t="s" s="15">
-        <v>96</v>
-      </c>
-      <c r="C41" t="s" s="15">
+      <c r="E41" s="2"/>
+    </row>
+    <row r="42" ht="15.65" customHeight="1">
+      <c r="A42" s="2"/>
+      <c r="B42" t="s" s="4">
+        <v>98</v>
+      </c>
+      <c r="C42" t="s" s="4">
         <v>101</v>
       </c>
-      <c r="D41" t="s" s="16">
+      <c r="D42" t="s" s="4">
         <v>102</v>
       </c>
-      <c r="E41" s="2"/>
-    </row>
-    <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="12"/>
-      <c r="B42" t="s" s="15">
-        <v>96</v>
-      </c>
-      <c r="C42" t="s" s="15">
+      <c r="E42" s="2"/>
+    </row>
+    <row r="43" ht="15.65" customHeight="1">
+      <c r="A43" s="2"/>
+      <c r="B43" t="s" s="4">
         <v>103</v>
       </c>
-      <c r="D42" t="s" s="16">
+      <c r="C43" t="s" s="4">
         <v>104</v>
       </c>
-      <c r="E42" s="2"/>
-    </row>
-    <row r="43" ht="13.65" customHeight="1">
-      <c r="A43" s="12"/>
-      <c r="B43" t="s" s="15">
+      <c r="D43" t="s" s="4">
         <v>105</v>
       </c>
-      <c r="C43" t="s" s="15">
+      <c r="E43" s="2"/>
+    </row>
+    <row r="44" ht="15.65" customHeight="1">
+      <c r="A44" s="2"/>
+      <c r="B44" t="s" s="4">
         <v>106</v>
       </c>
-      <c r="D43" t="s" s="17">
+      <c r="C44" t="s" s="4">
+        <v>92</v>
+      </c>
+      <c r="D44" t="s" s="4">
         <v>107</v>
       </c>
-      <c r="E43" s="2"/>
-    </row>
-    <row r="44" ht="13.65" customHeight="1">
-      <c r="A44" s="12"/>
-      <c r="B44" t="s" s="15">
-        <v>105</v>
-      </c>
-      <c r="C44" t="s" s="15">
+      <c r="E44" s="2"/>
+    </row>
+    <row r="45" ht="15.65" customHeight="1">
+      <c r="A45" s="2"/>
+      <c r="B45" t="s" s="4">
         <v>108</v>
       </c>
-      <c r="D44" t="s" s="17">
+      <c r="C45" t="s" s="4">
         <v>109</v>
       </c>
-      <c r="E44" s="2"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="12"/>
-      <c r="B45" t="s" s="15">
+      <c r="D45" t="s" s="4">
         <v>110</v>
       </c>
-      <c r="C45" t="s" s="15">
+      <c r="E45" s="2"/>
+    </row>
+    <row r="46" ht="15.65" customHeight="1">
+      <c r="A46" s="2"/>
+      <c r="B46" t="s" s="4">
         <v>111</v>
       </c>
-      <c r="D45" t="s" s="16">
+      <c r="C46" t="s" s="4">
         <v>112</v>
       </c>
-      <c r="E45" s="2"/>
-    </row>
-    <row r="46" ht="13.65" customHeight="1">
-      <c r="A46" s="2"/>
-      <c r="B46" t="s" s="18">
-        <v>67</v>
-      </c>
-      <c r="C46" t="s" s="18">
+      <c r="D46" t="s" s="4">
         <v>113</v>
       </c>
-      <c r="D46" t="s" s="19">
+      <c r="E46" s="2"/>
+    </row>
+    <row r="47" ht="15.65" customHeight="1">
+      <c r="A47" s="2"/>
+      <c r="B47" t="s" s="4">
         <v>114</v>
       </c>
-      <c r="E46" s="2"/>
-    </row>
-    <row r="47" ht="13.65" customHeight="1">
-      <c r="A47" s="2"/>
-      <c r="B47" s="20"/>
-      <c r="C47" s="21"/>
-      <c r="D47" s="22"/>
+      <c r="C47" t="s" s="4">
+        <v>115</v>
+      </c>
+      <c r="D47" t="s" s="4">
+        <v>116</v>
+      </c>
       <c r="E47" s="2"/>
     </row>
-    <row r="48" ht="13.65" customHeight="1">
+    <row r="48" ht="15.65" customHeight="1">
       <c r="A48" s="2"/>
-      <c r="B48" s="20"/>
-      <c r="C48" s="21"/>
-      <c r="D48" s="22"/>
+      <c r="B48" t="s" s="4">
+        <v>114</v>
+      </c>
+      <c r="C48" t="s" s="4">
+        <v>117</v>
+      </c>
+      <c r="D48" t="s" s="4">
+        <v>118</v>
+      </c>
       <c r="E48" s="2"/>
+    </row>
+    <row r="49" ht="15.65" customHeight="1">
+      <c r="A49" s="2"/>
+      <c r="B49" t="s" s="4">
+        <v>114</v>
+      </c>
+      <c r="C49" t="s" s="4">
+        <v>119</v>
+      </c>
+      <c r="D49" t="s" s="4">
+        <v>120</v>
+      </c>
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" ht="15.65" customHeight="1">
+      <c r="A50" s="2"/>
+      <c r="B50" t="s" s="4">
+        <v>114</v>
+      </c>
+      <c r="C50" t="s" s="4">
+        <v>121</v>
+      </c>
+      <c r="D50" t="s" s="4">
+        <v>122</v>
+      </c>
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" ht="15.65" customHeight="1">
+      <c r="A51" s="2"/>
+      <c r="B51" t="s" s="4">
+        <v>123</v>
+      </c>
+      <c r="C51" t="s" s="4">
+        <v>124</v>
+      </c>
+      <c r="D51" t="s" s="4">
+        <v>125</v>
+      </c>
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" ht="15.65" customHeight="1">
+      <c r="A52" s="2"/>
+      <c r="B52" t="s" s="4">
+        <v>126</v>
+      </c>
+      <c r="C52" t="s" s="4">
+        <v>127</v>
+      </c>
+      <c r="D52" t="s" s="4">
+        <v>128</v>
+      </c>
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" ht="15.65" customHeight="1">
+      <c r="A53" s="2"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="5"/>
+      <c r="E53" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.25" footer="0.25"/>
